--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2018_aysen.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2018_aysen.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:46</t>
+    <t xml:space="preserve">2026-10-05 02:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>289757.69</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -847,7 +847,7 @@
         <v>297668.06</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>303464.09</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1031,7 +1031,7 @@
         <v>33</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>297001.12</v>
+        <v>297001.13</v>
       </c>
       <c r="C32" s="2" t="n">
         <v>305187.22</v>
@@ -1287,7 +1287,7 @@
         <v>367522.34</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1416,7 +1416,7 @@
         <v>68</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>409552.12</v>
+        <v>409552.13</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>432824.94</v>
@@ -1529,7 +1529,7 @@
         <v>413887.09</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>436203.56</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
